--- a/artfynd/A 57599-2025 artfynd.xlsx
+++ b/artfynd/A 57599-2025 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130155434</v>
+        <v>130155435</v>
       </c>
       <c r="B7" t="n">
-        <v>57662</v>
+        <v>57900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603266</v>
+        <v>603514</v>
       </c>
       <c r="R7" t="n">
-        <v>6525585</v>
+        <v>6525586</v>
       </c>
       <c r="S7" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130155435</v>
+        <v>130155434</v>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603514</v>
+        <v>603266</v>
       </c>
       <c r="R8" t="n">
-        <v>6525586</v>
+        <v>6525585</v>
       </c>
       <c r="S8" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 57599-2025 artfynd.xlsx
+++ b/artfynd/A 57599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130155447</v>
       </c>
       <c r="B2" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>130155443</v>
       </c>
       <c r="B5" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>130155441</v>
       </c>
       <c r="B6" t="n">
-        <v>91412</v>
+        <v>91414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130155435</v>
+        <v>130155434</v>
       </c>
       <c r="B7" t="n">
-        <v>57900</v>
+        <v>57662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603514</v>
+        <v>603266</v>
       </c>
       <c r="R7" t="n">
-        <v>6525586</v>
+        <v>6525585</v>
       </c>
       <c r="S7" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130155434</v>
+        <v>130155435</v>
       </c>
       <c r="B8" t="n">
-        <v>57662</v>
+        <v>57900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603266</v>
+        <v>603514</v>
       </c>
       <c r="R8" t="n">
-        <v>6525585</v>
+        <v>6525586</v>
       </c>
       <c r="S8" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 57599-2025 artfynd.xlsx
+++ b/artfynd/A 57599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130155447</v>
       </c>
       <c r="B2" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>130155436</v>
       </c>
       <c r="B3" t="n">
-        <v>78498</v>
+        <v>78583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1020,32 +1020,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130155443</v>
+        <v>130155441</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>91501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603645</v>
+        <v>603578</v>
       </c>
       <c r="R5" t="n">
-        <v>6525594</v>
+        <v>6525567</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,12 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,32 +1130,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130155441</v>
+        <v>130155443</v>
       </c>
       <c r="B6" t="n">
-        <v>91414</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603578</v>
+        <v>603645</v>
       </c>
       <c r="R6" t="n">
-        <v>6525567</v>
+        <v>6525594</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130155434</v>
+        <v>130155435</v>
       </c>
       <c r="B7" t="n">
-        <v>57662</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603266</v>
+        <v>603514</v>
       </c>
       <c r="R7" t="n">
-        <v>6525585</v>
+        <v>6525586</v>
       </c>
       <c r="S7" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130155435</v>
+        <v>130155434</v>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57747</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603514</v>
+        <v>603266</v>
       </c>
       <c r="R8" t="n">
-        <v>6525586</v>
+        <v>6525585</v>
       </c>
       <c r="S8" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 57599-2025 artfynd.xlsx
+++ b/artfynd/A 57599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130155447</v>
       </c>
       <c r="B2" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>130155436</v>
       </c>
       <c r="B3" t="n">
-        <v>78583</v>
+        <v>78586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>130155443</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>130155441</v>
       </c>
       <c r="B6" t="n">
-        <v>91501</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130155435</v>
+        <v>130155434</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>57747</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603514</v>
+        <v>603266</v>
       </c>
       <c r="R7" t="n">
-        <v>6525586</v>
+        <v>6525585</v>
       </c>
       <c r="S7" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130155434</v>
+        <v>130155435</v>
       </c>
       <c r="B8" t="n">
-        <v>57747</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603266</v>
+        <v>603514</v>
       </c>
       <c r="R8" t="n">
-        <v>6525585</v>
+        <v>6525586</v>
       </c>
       <c r="S8" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 57599-2025 artfynd.xlsx
+++ b/artfynd/A 57599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130155447</v>
       </c>
       <c r="B2" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>130155436</v>
       </c>
       <c r="B3" t="n">
-        <v>78586</v>
+        <v>78612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>130155443</v>
       </c>
       <c r="B5" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>130155441</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>130155434</v>
       </c>
       <c r="B7" t="n">
-        <v>57747</v>
+        <v>57773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>130155435</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57599-2025 artfynd.xlsx
+++ b/artfynd/A 57599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130155447</v>
       </c>
       <c r="B2" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>130155443</v>
       </c>
       <c r="B5" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>130155441</v>
       </c>
       <c r="B6" t="n">
-        <v>91530</v>
+        <v>91531</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57599-2025 artfynd.xlsx
+++ b/artfynd/A 57599-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130155447</v>
       </c>
       <c r="B2" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>130155443</v>
       </c>
       <c r="B5" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>130155441</v>
       </c>
       <c r="B6" t="n">
-        <v>91531</v>
+        <v>91532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57599-2025 artfynd.xlsx
+++ b/artfynd/A 57599-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130155447</v>
+        <v>130155443</v>
       </c>
       <c r="B2" t="n">
-        <v>106018</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603236</v>
+        <v>603645</v>
       </c>
       <c r="R2" t="n">
-        <v>6525617</v>
+        <v>6525594</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130155436</v>
+        <v>130155441</v>
       </c>
       <c r="B3" t="n">
-        <v>78612</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603328</v>
+        <v>603578</v>
       </c>
       <c r="R3" t="n">
-        <v>6525635</v>
+        <v>6525567</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,61 +900,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130155433</v>
+        <v>130155436</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormossen, Srm</t>
+          <t>Stormossen, Stormossen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603240</v>
+        <v>603328</v>
       </c>
       <c r="R4" t="n">
-        <v>6525615</v>
+        <v>6525635</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,37 +1010,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130155443</v>
+        <v>130155434</v>
       </c>
       <c r="B5" t="n">
-        <v>92212</v>
+        <v>57874</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603645</v>
+        <v>603266</v>
       </c>
       <c r="R5" t="n">
-        <v>6525594</v>
+        <v>6525585</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,12 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130155441</v>
+        <v>130155433</v>
       </c>
       <c r="B6" t="n">
-        <v>91532</v>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,40 +1140,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormossen, Stormossen, Srm</t>
+          <t>Stormossen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603578</v>
+        <v>603240</v>
       </c>
       <c r="R6" t="n">
-        <v>6525567</v>
+        <v>6525615</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130155434</v>
+        <v>130155435</v>
       </c>
       <c r="B7" t="n">
-        <v>57773</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1292,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603266</v>
+        <v>603514</v>
       </c>
       <c r="R7" t="n">
-        <v>6525585</v>
+        <v>6525586</v>
       </c>
       <c r="S7" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,46 +1368,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130155435</v>
+        <v>130155447</v>
       </c>
       <c r="B8" t="n">
-        <v>58011</v>
+        <v>106243</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603514</v>
+        <v>603236</v>
       </c>
       <c r="R8" t="n">
-        <v>6525586</v>
+        <v>6525617</v>
       </c>
       <c r="S8" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 57599-2025 artfynd.xlsx
+++ b/artfynd/A 57599-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155443</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155441</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155436</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155434</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155433</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,6 +1395,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155435</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,8 +1515,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155447</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>